--- a/facit/StructureDefinition-SkyddadIdentitet.xlsx
+++ b/facit/StructureDefinition-SkyddadIdentitet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-30T09:46:55+00:00</t>
+    <t>2026-10-30T09:59:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/facit/StructureDefinition-SkyddadIdentitet.xlsx
+++ b/facit/StructureDefinition-SkyddadIdentitet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-30T09:59:27+00:00</t>
+    <t>2026-10-30T10:06:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
